--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -5081,7 +5081,7 @@
         <v>0</v>
       </c>
       <c r="I108" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5637,10 +5637,10 @@
         <v>0.465101</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -5898,7 +5898,7 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -6027,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>1</v>
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J151" t="n">
         <v>1</v>
@@ -8991,10 +8991,10 @@
         <v>0.803191</v>
       </c>
       <c r="H199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I199" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J199" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/Virchow2/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -514,10 +514,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.579889</v>
+        <v>0.237598</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.92562</v>
+        <v>0.9654160000000001</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.401762</v>
+        <v>0.284377</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.417094</v>
+        <v>0.420119</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.418064</v>
+        <v>0.199902</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.597015</v>
+        <v>0.606722</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -772,10 +772,10 @@
         <v>0.002178</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.513207</v>
+        <v>0.462694</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.474874</v>
+        <v>0.333599</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.474327</v>
+        <v>0.453884</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.232614</v>
+        <v>0.142376</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.71346</v>
+        <v>0.7334889999999999</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -987,10 +987,10 @@
         <v>8e-06</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.606992</v>
+        <v>0.410774</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.453773</v>
+        <v>0.298778</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.328704</v>
+        <v>0.214808</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.424486</v>
+        <v>0.277505</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.470759</v>
+        <v>0.339629</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.287859</v>
+        <v>0.190937</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.289434</v>
+        <v>0.257432</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.25727</v>
+        <v>0.309987</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.27303</v>
+        <v>0.201187</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.763139</v>
+        <v>0.855979</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.379787</v>
+        <v>0.228898</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.324478</v>
+        <v>0.236223</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.302723</v>
+        <v>0.260428</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.440595</v>
+        <v>0.346523</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.305793</v>
+        <v>0.344694</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.448345</v>
+        <v>0.30209</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.655384</v>
+        <v>0.553327</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.448398</v>
+        <v>0.309484</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.336458</v>
+        <v>0.241483</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.412152</v>
+        <v>0.392344</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.360373</v>
+        <v>0.229985</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.6633829999999999</v>
+        <v>0.573408</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.405177</v>
+        <v>0.234113</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.409143</v>
+        <v>0.269297</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.292482</v>
+        <v>0.222317</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.397811</v>
+        <v>0.346219</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.245353</v>
+        <v>0.117333</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2148,10 +2148,10 @@
         <v>0.001039</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.453305</v>
+        <v>0.538594</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.319922</v>
+        <v>0.19264</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.241964</v>
+        <v>0.191384</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.347999</v>
+        <v>0.157103</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.311624</v>
+        <v>0.281355</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.466342</v>
+        <v>0.325332</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2406,10 +2406,10 @@
         <v>0.00134</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.577506</v>
+        <v>0.44981</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.348052</v>
+        <v>0.168102</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2492,10 +2492,10 @@
         <v>0.000139</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.448078</v>
+        <v>0.501337</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.407712</v>
+        <v>0.311696</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2578,10 +2578,10 @@
         <v>0.117943</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.456763</v>
+        <v>0.5423519999999999</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
@@ -2621,10 +2621,10 @@
         <v>1.5e-05</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.541693</v>
+        <v>0.455899</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.846726</v>
+        <v>0.866703</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2707,10 +2707,10 @@
         <v>1e-06</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.51562</v>
+        <v>0.357895</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.663173</v>
+        <v>0.628312</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.659483</v>
+        <v>0.7830279999999999</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.348531</v>
+        <v>0.271993</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>0.022183</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.598391</v>
+        <v>0.434558</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.434926</v>
+        <v>0.264701</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.46857</v>
+        <v>0.5928870000000001</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.858139</v>
+        <v>0.87183</v>
       </c>
       <c r="H60" t="n">
         <v>1</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.969511</v>
+        <v>0.991334</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.221634</v>
+        <v>0.2756</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.953698</v>
+        <v>0.989143</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3180,10 +3180,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.505966</v>
+        <v>0.456507</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.424237</v>
+        <v>0.386243</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.227725</v>
+        <v>0.206439</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.374477</v>
+        <v>0.391605</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.328124</v>
+        <v>0.338391</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.401322</v>
+        <v>0.38112</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.277263</v>
+        <v>0.260817</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.557252</v>
+        <v>0.54995</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.217044</v>
+        <v>0.181147</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.23921</v>
+        <v>0.165934</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.315905</v>
+        <v>0.200056</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0.498394</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.562991</v>
+        <v>0.456347</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3696,10 +3696,10 @@
         <v>0.005124</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.588741</v>
+        <v>0.446923</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.850473</v>
+        <v>0.907416</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.465934</v>
+        <v>0.374893</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.486524</v>
+        <v>0.337183</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.372649</v>
+        <v>0.245399</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.361936</v>
+        <v>0.198199</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.873752</v>
+        <v>0.921347</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5679920000000001</v>
+        <v>0.659534</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.237956</v>
+        <v>0.182866</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.325484</v>
+        <v>0.275072</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.284771</v>
+        <v>0.133023</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.287695</v>
+        <v>0.181902</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.281309</v>
+        <v>0.171685</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.837963</v>
+        <v>0.881958</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.192654</v>
+        <v>0.072557</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.312509</v>
+        <v>0.192912</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.454343</v>
+        <v>0.315248</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4427,10 +4427,10 @@
         <v>1e-06</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.544569</v>
+        <v>0.351047</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.408754</v>
+        <v>0.225926</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.36823</v>
+        <v>0.15752</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>0.556076</v>
+        <v>0.517502</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.260395</v>
+        <v>0.155084</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.6178439999999999</v>
+        <v>0.692092</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.764675</v>
+        <v>0.727244</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>1</v>
       </c>
       <c r="G100" t="n">
-        <v>0.500108</v>
+        <v>0.595789</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.832985</v>
+        <v>0.956878</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.97406</v>
+        <v>0.998169</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.666964</v>
+        <v>0.594672</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.372347</v>
+        <v>0.275465</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.193233</v>
+        <v>0.08035200000000001</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.273685</v>
+        <v>0.107098</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.243914</v>
+        <v>0.175821</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.946939</v>
+        <v>0.984333</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.270739</v>
+        <v>0.237452</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.918174</v>
+        <v>0.903724</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.167943</v>
+        <v>0.056985</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.283121</v>
+        <v>0.163083</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.256976</v>
+        <v>0.10671</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.18224</v>
+        <v>0.128974</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.315792</v>
+        <v>0.249255</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.258357</v>
+        <v>0.155089</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.441533</v>
+        <v>0.298731</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.221127</v>
+        <v>0.110099</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0.328861</v>
+        <v>0.231316</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.209202</v>
+        <v>0.12286</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.465101</v>
+        <v>0.333473</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.850927</v>
+        <v>0.885105</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>0</v>
       </c>
       <c r="G123" t="n">
-        <v>0.453295</v>
+        <v>0.372937</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.248921</v>
+        <v>0.114589</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.223152</v>
+        <v>0.126087</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.253726</v>
+        <v>0.161605</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.145823</v>
+        <v>0.052524</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.238224</v>
+        <v>0.155418</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.403961</v>
+        <v>0.326411</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.395211</v>
+        <v>0.454069</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.200368</v>
+        <v>0.155571</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.162221</v>
+        <v>0.083719</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.329252</v>
+        <v>0.265902</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.355552</v>
+        <v>0.188679</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.145034</v>
+        <v>0.123301</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.176501</v>
+        <v>0.06683600000000001</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.211443</v>
+        <v>0.102036</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.192928</v>
+        <v>0.071455</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.234293</v>
+        <v>0.144058</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.163413</v>
+        <v>0.074892</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.223112</v>
+        <v>0.108301</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.249843</v>
+        <v>0.129988</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.210129</v>
+        <v>0.156014</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.324033</v>
+        <v>0.272887</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.257917</v>
+        <v>0.172522</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.291035</v>
+        <v>0.211362</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.423585</v>
+        <v>0.402961</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.198342</v>
+        <v>0.057226</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.276175</v>
+        <v>0.224031</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.221616</v>
+        <v>0.087369</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.765529</v>
+        <v>0.671855</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.996796</v>
+        <v>0.99941</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.211483</v>
+        <v>0.11304</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.247336</v>
+        <v>0.219116</v>
       </c>
       <c r="H154" t="n">
         <v>1</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.317654</v>
+        <v>0.244391</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.365891</v>
+        <v>0.223764</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7179,10 +7179,10 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.42569</v>
+        <v>0.624667</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.471536</v>
+        <v>0.333148</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.341982</v>
+        <v>0.193928</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.267499</v>
+        <v>0.202141</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.375444</v>
+        <v>0.255776</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.280298</v>
+        <v>0.184967</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.607446</v>
+        <v>0.538435</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.152715</v>
+        <v>0.060489</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.313555</v>
+        <v>0.137749</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.493997</v>
+        <v>0.385562</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.249424</v>
+        <v>0.138698</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.807859</v>
+        <v>0.725353</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.243092</v>
+        <v>0.116633</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.242815</v>
+        <v>0.246879</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.320599</v>
+        <v>0.171026</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.375572</v>
+        <v>0.213548</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.184793</v>
+        <v>0.111839</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.129103</v>
+        <v>0.053465</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.378939</v>
+        <v>0.229456</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.447481</v>
+        <v>0.309733</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.162765</v>
+        <v>0.055911</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.255385</v>
+        <v>0.132821</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.171727</v>
+        <v>0.067791</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.16</v>
+        <v>0.052243</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.155146</v>
+        <v>0.122873</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.399705</v>
+        <v>0.284847</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.150337</v>
+        <v>0.035168</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.161133</v>
+        <v>0.077746</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.256424</v>
+        <v>0.138674</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.231703</v>
+        <v>0.09740500000000001</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.340755</v>
+        <v>0.143861</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.300042</v>
+        <v>0.196974</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.19894</v>
+        <v>0.092624</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8598,10 +8598,10 @@
         <v>0.8960900000000001</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.524596</v>
+        <v>0.439884</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.737087</v>
+        <v>0.810658</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>0.60573</v>
+        <v>0.580949</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.48835</v>
+        <v>0.407962</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.237462</v>
+        <v>0.137754</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.303742</v>
+        <v>0.138318</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.211468</v>
+        <v>0.262175</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.801962</v>
+        <v>0.878342</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.974619</v>
+        <v>0.99116</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.803191</v>
+        <v>0.828199</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.454627</v>
+        <v>0.340824</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.351383</v>
+        <v>0.173122</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.128277</v>
+        <v>0.034945</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.203949</v>
+        <v>0.082924</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.173257</v>
+        <v>0.131241</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.280456</v>
+        <v>0.24271</v>
       </c>
       <c r="H317" t="n">
         <v>1</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.354355</v>
+        <v>0.336122</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.210046</v>
+        <v>0.123844</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.984911</v>
+        <v>0.996573</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.327793</v>
+        <v>0.180042</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14274,10 +14274,10 @@
         <v>0.000526</v>
       </c>
       <c r="F322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.647421</v>
+        <v>0.452373</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.223423</v>
+        <v>0.066214</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.280973</v>
+        <v>0.123998</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.163774</v>
+        <v>0.086849</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.208472</v>
+        <v>0.09128600000000001</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.317141</v>
+        <v>0.154489</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.689255</v>
+        <v>0.738441</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.217207</v>
+        <v>0.068717</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.225746</v>
+        <v>0.076594</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14661,10 +14661,10 @@
         <v>0.931227</v>
       </c>
       <c r="F331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G331" t="n">
-        <v>0.591838</v>
+        <v>0.302678</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.242339</v>
+        <v>0.06877900000000001</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.996041</v>
+        <v>0.999718</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.496285</v>
+        <v>0.343332</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.160511</v>
+        <v>0.081542</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14876,10 +14876,10 @@
         <v>0.791848</v>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.59671</v>
+        <v>0.466971</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.210093</v>
+        <v>0.08786099999999999</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.222531</v>
+        <v>0.07131</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.206402</v>
+        <v>0.045116</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.145889</v>
+        <v>0.060573</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.188042</v>
+        <v>0.057811</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.104866</v>
+        <v>0.0338</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.121037</v>
+        <v>0.035151</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.111497</v>
+        <v>0.040879</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0.283227</v>
+        <v>0.15556</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.332816</v>
+        <v>0.147184</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.368698</v>
+        <v>0.113394</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.468522</v>
+        <v>0.193341</v>
       </c>
       <c r="H348" t="n">
         <v>1</v>
@@ -15435,10 +15435,10 @@
         <v>0.004745</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.51652</v>
+        <v>0.379111</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.792024</v>
+        <v>0.943654</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.271981</v>
+        <v>0.136026</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.256075</v>
+        <v>0.109838</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.129452</v>
+        <v>0.07524500000000001</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.243778</v>
+        <v>0.158275</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.148932</v>
+        <v>0.058716</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.116929</v>
+        <v>0.055777</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.200681</v>
+        <v>0.064942</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0.195365</v>
+        <v>0.074364</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.166789</v>
+        <v>0.047784</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.413467</v>
+        <v>0.294284</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.263162</v>
+        <v>0.169982</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.941235</v>
+        <v>0.986351</v>
       </c>
       <c r="H362" t="n">
         <v>1</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.159969</v>
+        <v>0.039712</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.940823</v>
+        <v>0.954949</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.141604</v>
+        <v>0.047734</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.113817</v>
+        <v>0.023709</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.277635</v>
+        <v>0.223928</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.273536</v>
+        <v>0.109331</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0.694966</v>
+        <v>0.644144</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.231071</v>
+        <v>0.066287</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>1</v>
       </c>
       <c r="G371" t="n">
-        <v>0.962601</v>
+        <v>0.9958360000000001</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.204986</v>
+        <v>0.071147</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.386123</v>
+        <v>0.251683</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.235095</v>
+        <v>0.090194</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.176303</v>
+        <v>0.099717</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.277095</v>
+        <v>0.108674</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.469869</v>
+        <v>0.261027</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.276407</v>
+        <v>0.18858</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.264779</v>
+        <v>0.082494</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.621301</v>
+        <v>0.796023</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.356497</v>
+        <v>0.086076</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16854,10 +16854,10 @@
         <v>0.000215</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G382" t="n">
-        <v>0.438671</v>
+        <v>0.7427510000000001</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.151164</v>
+        <v>0.056888</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.404316</v>
+        <v>0.240739</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.076584</v>
+        <v>0.022793</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.112076</v>
+        <v>0.031888</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.246602</v>
+        <v>0.103496</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.348398</v>
+        <v>0.225179</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.207362</v>
+        <v>0.043671</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.191458</v>
+        <v>0.091859</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.170642</v>
+        <v>0.094273</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.737146</v>
+        <v>0.545717</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="G393" t="n">
-        <v>0.458287</v>
+        <v>0.324888</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.206442</v>
+        <v>0.08920599999999999</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.752735</v>
+        <v>0.648547</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.258789</v>
+        <v>0.110461</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.287603</v>
+        <v>0.175873</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.29962</v>
+        <v>0.197364</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.238263</v>
+        <v>0.132249</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.22079</v>
+        <v>0.106852</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0.657924</v>
+        <v>0.758493</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.122614</v>
+        <v>0.052199</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.8355399999999999</v>
+        <v>0.888602</v>
       </c>
       <c r="H403" t="n">
         <v>1</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.174199</v>
+        <v>0.051538</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.115598</v>
+        <v>0.042918</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.303852</v>
+        <v>0.108405</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.684943</v>
+        <v>0.679773</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.852692</v>
+        <v>0.982663</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0.78365</v>
+        <v>0.694134</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.170271</v>
+        <v>0.036507</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.598167</v>
+        <v>0.5954159999999999</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.921153</v>
+        <v>0.948699</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.204111</v>
+        <v>0.128102</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.675813</v>
+        <v>0.836772</v>
       </c>
       <c r="H414" t="n">
         <v>0</v>
